--- a/data/analyze.xlsx
+++ b/data/analyze.xlsx
@@ -1,22 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bernhardtramat/Documents/Passkeys-OneDrive/code/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0E764C9-F12E-E746-A12B-2DE47139F4DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80077752-5B38-FC4B-BADC-F1639EB6DCA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17920" yWindow="500" windowWidth="17920" windowHeight="20260" xr2:uid="{83530D48-1C8D-1A42-8342-5184FF63D261}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="35840" windowHeight="20000" xr2:uid="{83530D48-1C8D-1A42-8342-5184FF63D261}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AF$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AG$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,12 +36,23 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Bernie</author>
+    <author>Author</author>
     <author>tc={0A8BEA4E-E311-8242-84AA-CA89B65F8357}</author>
   </authors>
   <commentList>
     <comment ref="Y20" authorId="0" shapeId="0" xr:uid="{833D2926-289A-E945-B82C-1786D6E3B03C}">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
         <r>
           <rPr>
             <sz val="10"/>
@@ -55,7 +61,7 @@
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">Bernie:
+          <t xml:space="preserve">
 Supoorts it but authentication failed </t>
         </r>
       </text>
@@ -64,13 +70,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Supports it but authentication fails. I wonder if this shold be a 2
 </t>
         </r>
@@ -80,13 +97,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Asks for verification once you visit account settings</t>
         </r>
       </text>
@@ -95,13 +123,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Only supports signing in with one passkey but let's you add multiple passkeys</t>
         </r>
       </text>
@@ -118,13 +157,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 I was able to set up the yubikey but I could not use it to sign in</t>
         </r>
       </text>
@@ -133,13 +183,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Should we check for user verification prior to updating passkeys?</t>
         </r>
       </text>
@@ -148,13 +209,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t xml:space="preserve">Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Not supported but allows you to sign in with it
 </t>
         </r>
@@ -164,13 +236,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Not supported but allows you to sign in with it</t>
         </r>
       </text>
@@ -179,13 +262,24 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Aptos Narrow"/>
             <family val="2"/>
             <scheme val="minor"/>
           </rPr>
-          <t>Bernie:
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
 Doesn't let you set up a cross device but lets you sign in with one.</t>
         </r>
       </text>
@@ -195,7 +289,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="268">
   <si>
     <t>Cluster</t>
   </si>
@@ -902,33 +996,15 @@
     <t>Priority 2</t>
   </si>
   <si>
-    <t>Security-Keys-Awareness 2</t>
-  </si>
-  <si>
     <t>Educational-Resources 3</t>
   </si>
   <si>
     <t>Naming-Conventions 2</t>
   </si>
   <si>
-    <t>Registration-Flow-Setup 3</t>
-  </si>
-  <si>
-    <t>OTP-Flow-Setup 3</t>
-  </si>
-  <si>
-    <t>Account-Settings-Setup 2</t>
-  </si>
-  <si>
-    <t>Security-Key-Setup 2</t>
-  </si>
-  <si>
     <t>Cross-Device-Setup 2</t>
   </si>
   <si>
-    <t>Account-Recovery-Setup 3</t>
-  </si>
-  <si>
     <t>Multiselection 2</t>
   </si>
   <si>
@@ -950,27 +1026,15 @@
     <t>Autofill-Feature 2</t>
   </si>
   <si>
-    <t>Fallback-Authentication-Options 2</t>
-  </si>
-  <si>
     <t>Cross-Device-Usage 3</t>
   </si>
   <si>
-    <t>Security-Key-Usage 3</t>
-  </si>
-  <si>
-    <t>Multi-Platform-Support 3</t>
-  </si>
-  <si>
     <t>Management-UI 2</t>
   </si>
   <si>
     <t>Delete-Option 2</t>
   </si>
   <si>
-    <t>Authenticator-Clean-Up 3</t>
-  </si>
-  <si>
     <t>Deletion-Authentication 4</t>
   </si>
   <si>
@@ -996,13 +1060,46 @@
   </si>
   <si>
     <t>Entertainment</t>
+  </si>
+  <si>
+    <t>Deletion-Confirmation 4</t>
+  </si>
+  <si>
+    <t>FSK-Awareness 2</t>
+  </si>
+  <si>
+    <t>Registration-Setup 3</t>
+  </si>
+  <si>
+    <t>OTP-Setup 3</t>
+  </si>
+  <si>
+    <t>Settings-Setup 2</t>
+  </si>
+  <si>
+    <t>FSK-Setup 2</t>
+  </si>
+  <si>
+    <t>Recovery-Setup 3</t>
+  </si>
+  <si>
+    <t>Fallback-Authentication 2</t>
+  </si>
+  <si>
+    <t>FSK-Usage 3</t>
+  </si>
+  <si>
+    <t>Multi-Platform-Usage 3</t>
+  </si>
+  <si>
+    <t>Authenticator-Cleanup 3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1043,6 +1140,14 @@
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1065,7 +1170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1077,6 +1182,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1096,9 +1202,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Bernhardt Ramat" id="{713FF208-C1F7-B449-9199-DA2821A34812}" userId="S::bramat@byu.edu::3d18751c-c21a-48d9-bf48-dfdddc6a88cf" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1418,7 +1522,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D62" dT="2025-03-30T03:48:57.27" personId="{713FF208-C1F7-B449-9199-DA2821A34812}" id="{0A8BEA4E-E311-8242-84AA-CA89B65F8357}">
+  <threadedComment ref="D62" dT="2025-03-30T03:48:57.27" personId="{00000000-0000-0000-0000-000000000000}" id="{0A8BEA4E-E311-8242-84AA-CA89B65F8357}">
     <text>Site neither has autofill nor Login CTA. Bad UX</text>
   </threadedComment>
 </ThreadedComments>
@@ -1426,13 +1530,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1FAB33D-8E6A-CD48-A4EC-22CBB3EAF02F}">
-  <dimension ref="A1:AF112"/>
+  <dimension ref="A1:AG112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="40.83203125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="40.83203125" style="2"/>
+    <col min="1" max="32" width="40.83203125" style="2"/>
+    <col min="33" max="33" width="40.83203125" style="5"/>
+    <col min="34" max="16384" width="40.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>232</v>
       </c>
@@ -1455,82 +1561,85 @@
         <v>234</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="X1" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="AE1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="2" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
@@ -1627,8 +1736,11 @@
       <c r="AF2" s="3">
         <v>3</v>
       </c>
+      <c r="AG2" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="3" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>145</v>
       </c>
@@ -1725,8 +1837,11 @@
       <c r="AF3" s="3">
         <v>3</v>
       </c>
+      <c r="AG3" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1823,8 +1938,11 @@
       <c r="AF4" s="3">
         <v>3</v>
       </c>
+      <c r="AG4" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="5" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>110</v>
       </c>
@@ -1921,8 +2039,11 @@
       <c r="AF5" s="3">
         <v>1</v>
       </c>
+      <c r="AG5" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>85</v>
       </c>
@@ -2019,8 +2140,11 @@
       <c r="AF6" s="3">
         <v>3</v>
       </c>
+      <c r="AG6" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>203</v>
       </c>
@@ -2117,8 +2241,11 @@
       <c r="AF7" s="3">
         <v>3</v>
       </c>
+      <c r="AG7" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>197</v>
       </c>
@@ -2132,7 +2259,7 @@
         <v>198</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
@@ -2215,8 +2342,11 @@
       <c r="AF8" s="3">
         <v>1</v>
       </c>
+      <c r="AG8" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>171</v>
       </c>
@@ -2313,8 +2443,11 @@
       <c r="AF9" s="3">
         <v>3</v>
       </c>
+      <c r="AG9" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>47</v>
       </c>
@@ -2411,8 +2544,11 @@
       <c r="AF10" s="3">
         <v>3</v>
       </c>
+      <c r="AG10" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>108</v>
       </c>
@@ -2509,8 +2645,11 @@
       <c r="AF11" s="3">
         <v>3</v>
       </c>
+      <c r="AG11" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>75</v>
       </c>
@@ -2607,8 +2746,11 @@
       <c r="AF12" s="3">
         <v>3</v>
       </c>
+      <c r="AG12" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>104</v>
       </c>
@@ -2622,7 +2764,7 @@
         <v>105</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F13" s="3">
         <v>3</v>
@@ -2705,8 +2847,11 @@
       <c r="AF13" s="3">
         <v>3</v>
       </c>
+      <c r="AG13" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="14" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>33</v>
       </c>
@@ -2720,7 +2865,7 @@
         <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F14" s="3">
         <v>3</v>
@@ -2803,8 +2948,11 @@
       <c r="AF14" s="3">
         <v>3</v>
       </c>
+      <c r="AG14" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="15" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>94</v>
       </c>
@@ -2901,8 +3049,11 @@
       <c r="AF15" s="3">
         <v>1</v>
       </c>
+      <c r="AG15" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="16" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>151</v>
       </c>
@@ -2999,8 +3150,11 @@
       <c r="AF16" s="3">
         <v>3</v>
       </c>
+      <c r="AG16" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="17" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>57</v>
       </c>
@@ -3097,8 +3251,11 @@
       <c r="AF17" s="3">
         <v>3</v>
       </c>
+      <c r="AG17" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="18" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>205</v>
       </c>
@@ -3195,8 +3352,11 @@
       <c r="AF18" s="3">
         <v>1</v>
       </c>
+      <c r="AG18" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="19" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>173</v>
       </c>
@@ -3210,7 +3370,7 @@
         <v>174</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F19" s="3">
         <v>3</v>
@@ -3293,8 +3453,11 @@
       <c r="AF19" s="3">
         <v>1</v>
       </c>
+      <c r="AG19" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="20" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>123</v>
       </c>
@@ -3391,8 +3554,11 @@
       <c r="AF20" s="3">
         <v>3</v>
       </c>
+      <c r="AG20" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="21" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>207</v>
       </c>
@@ -3489,8 +3655,11 @@
       <c r="AF21" s="3">
         <v>1</v>
       </c>
+      <c r="AG21" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="22" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>139</v>
       </c>
@@ -3587,8 +3756,11 @@
       <c r="AF22" s="3">
         <v>1</v>
       </c>
+      <c r="AG22" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="23" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>209</v>
       </c>
@@ -3685,8 +3857,11 @@
       <c r="AF23" s="3">
         <v>3</v>
       </c>
+      <c r="AG23" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="24" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>149</v>
       </c>
@@ -3783,8 +3958,11 @@
       <c r="AF24" s="3">
         <v>3</v>
       </c>
+      <c r="AG24" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="25" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>29</v>
       </c>
@@ -3798,7 +3976,7 @@
         <v>30</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F25" s="3">
         <v>3</v>
@@ -3881,8 +4059,11 @@
       <c r="AF25" s="3">
         <v>1</v>
       </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>98</v>
       </c>
@@ -3896,7 +4077,7 @@
         <v>99</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F26" s="3">
         <v>3</v>
@@ -3979,8 +4160,11 @@
       <c r="AF26" s="3">
         <v>1</v>
       </c>
+      <c r="AG26" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="27" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>195</v>
       </c>
@@ -3994,7 +4178,7 @@
         <v>196</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="F27" s="3">
         <v>3</v>
@@ -4077,8 +4261,11 @@
       <c r="AF27" s="3">
         <v>3</v>
       </c>
+      <c r="AG27" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="28" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>79</v>
       </c>
@@ -4175,8 +4362,11 @@
       <c r="AF28" s="3">
         <v>3</v>
       </c>
+      <c r="AG28" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>27</v>
       </c>
@@ -4273,8 +4463,11 @@
       <c r="AF29" s="3">
         <v>3</v>
       </c>
+      <c r="AG29" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="30" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>113</v>
       </c>
@@ -4288,7 +4481,7 @@
         <v>114</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F30" s="3">
         <v>3</v>
@@ -4371,8 +4564,11 @@
       <c r="AF30" s="3">
         <v>1</v>
       </c>
+      <c r="AG30" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>96</v>
       </c>
@@ -4469,8 +4665,11 @@
       <c r="AF31" s="3">
         <v>1</v>
       </c>
+      <c r="AG31" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="32" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>155</v>
       </c>
@@ -4567,8 +4766,11 @@
       <c r="AF32" s="3">
         <v>3</v>
       </c>
+      <c r="AG32" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>183</v>
       </c>
@@ -4665,8 +4867,11 @@
       <c r="AF33" s="3">
         <v>1</v>
       </c>
+      <c r="AG33" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="34" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>185</v>
       </c>
@@ -4763,8 +4968,11 @@
       <c r="AF34" s="3">
         <v>3</v>
       </c>
+      <c r="AG34" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="35" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>125</v>
       </c>
@@ -4861,8 +5069,11 @@
       <c r="AF35" s="3">
         <v>3</v>
       </c>
+      <c r="AG35" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="36" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>133</v>
       </c>
@@ -4876,7 +5087,7 @@
         <v>134</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F36" s="3">
         <v>3</v>
@@ -4959,8 +5170,11 @@
       <c r="AF36" s="3">
         <v>1</v>
       </c>
+      <c r="AG36" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="37" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>14</v>
       </c>
@@ -5057,8 +5271,11 @@
       <c r="AF37" s="3">
         <v>3</v>
       </c>
+      <c r="AG37" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>193</v>
       </c>
@@ -5155,8 +5372,11 @@
       <c r="AF38" s="3">
         <v>3</v>
       </c>
+      <c r="AG38" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="39" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>4</v>
       </c>
@@ -5253,8 +5473,11 @@
       <c r="AF39" s="3">
         <v>3</v>
       </c>
+      <c r="AG39" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="40" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>211</v>
       </c>
@@ -5351,8 +5574,11 @@
       <c r="AF40" s="3">
         <v>3</v>
       </c>
+      <c r="AG40" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="41" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>175</v>
       </c>
@@ -5366,7 +5592,7 @@
         <v>176</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F41" s="3">
         <v>3</v>
@@ -5449,8 +5675,11 @@
       <c r="AF41" s="3">
         <v>1</v>
       </c>
+      <c r="AG41" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="42" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>167</v>
       </c>
@@ -5547,8 +5776,11 @@
       <c r="AF42" s="3">
         <v>1</v>
       </c>
+      <c r="AG42" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="43" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>67</v>
       </c>
@@ -5645,8 +5877,11 @@
       <c r="AF43" s="3">
         <v>3</v>
       </c>
+      <c r="AG43" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="44" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>59</v>
       </c>
@@ -5743,8 +5978,11 @@
       <c r="AF44" s="3">
         <v>3</v>
       </c>
+      <c r="AG44" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="45" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>213</v>
       </c>
@@ -5841,8 +6079,11 @@
       <c r="AF45" s="3">
         <v>1</v>
       </c>
+      <c r="AG45" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="46" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>181</v>
       </c>
@@ -5939,8 +6180,11 @@
       <c r="AF46" s="3">
         <v>3</v>
       </c>
+      <c r="AG46" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="47" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>69</v>
       </c>
@@ -5954,7 +6198,7 @@
         <v>70</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F47" s="3">
         <v>3</v>
@@ -6037,8 +6281,11 @@
       <c r="AF47" s="3">
         <v>1</v>
       </c>
+      <c r="AG47" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="48" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>201</v>
       </c>
@@ -6135,8 +6382,11 @@
       <c r="AF48" s="3">
         <v>1</v>
       </c>
+      <c r="AG48" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>35</v>
       </c>
@@ -6233,8 +6483,11 @@
       <c r="AF49" s="3">
         <v>3</v>
       </c>
+      <c r="AG49" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="50" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>61</v>
       </c>
@@ -6331,8 +6584,11 @@
       <c r="AF50" s="3">
         <v>3</v>
       </c>
+      <c r="AG50" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="51" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>81</v>
       </c>
@@ -6429,8 +6685,11 @@
       <c r="AF51" s="3">
         <v>3</v>
       </c>
+      <c r="AG51" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="52" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>215</v>
       </c>
@@ -6527,8 +6786,11 @@
       <c r="AF52" s="3">
         <v>3</v>
       </c>
+      <c r="AG52" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="53" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>77</v>
       </c>
@@ -6542,7 +6804,7 @@
         <v>78</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F53" s="3">
         <v>3</v>
@@ -6625,8 +6887,11 @@
       <c r="AF53" s="3">
         <v>3</v>
       </c>
+      <c r="AG53" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="54" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>102</v>
       </c>
@@ -6723,8 +6988,11 @@
       <c r="AF54" s="3">
         <v>3</v>
       </c>
+      <c r="AG54" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="55" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>143</v>
       </c>
@@ -6821,8 +7089,11 @@
       <c r="AF55" s="3">
         <v>1</v>
       </c>
+      <c r="AG55" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="56" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>217</v>
       </c>
@@ -6836,7 +7107,7 @@
         <v>218</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F56" s="3">
         <v>1</v>
@@ -6919,8 +7190,11 @@
       <c r="AF56" s="3">
         <v>0</v>
       </c>
+      <c r="AG56" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>115</v>
       </c>
@@ -7017,8 +7291,11 @@
       <c r="AF57" s="3">
         <v>3</v>
       </c>
+      <c r="AG57" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="58" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>119</v>
       </c>
@@ -7115,8 +7392,11 @@
       <c r="AF58" s="3">
         <v>3</v>
       </c>
+      <c r="AG58" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="59" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>9</v>
       </c>
@@ -7130,7 +7410,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F59" s="3">
         <v>3</v>
@@ -7213,8 +7493,11 @@
       <c r="AF59" s="3">
         <v>1</v>
       </c>
+      <c r="AG59" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="60" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>121</v>
       </c>
@@ -7311,8 +7594,11 @@
       <c r="AF60" s="3">
         <v>1</v>
       </c>
+      <c r="AG60" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="61" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>191</v>
       </c>
@@ -7409,8 +7695,11 @@
       <c r="AF61" s="3">
         <v>3</v>
       </c>
+      <c r="AG61" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="62" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>219</v>
       </c>
@@ -7507,8 +7796,11 @@
       <c r="AF62" s="3">
         <v>3</v>
       </c>
+      <c r="AG62" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="63" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>135</v>
       </c>
@@ -7605,8 +7897,11 @@
       <c r="AF63" s="3">
         <v>3</v>
       </c>
+      <c r="AG63" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="64" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>161</v>
       </c>
@@ -7703,8 +7998,11 @@
       <c r="AF64" s="3">
         <v>1</v>
       </c>
+      <c r="AG64" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="65" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>153</v>
       </c>
@@ -7718,7 +8016,7 @@
         <v>154</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="F65" s="3">
         <v>3</v>
@@ -7801,8 +8099,11 @@
       <c r="AF65" s="3">
         <v>3</v>
       </c>
+      <c r="AG65" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="66" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>106</v>
       </c>
@@ -7899,8 +8200,11 @@
       <c r="AF66" s="3">
         <v>1</v>
       </c>
+      <c r="AG66" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="67" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>7</v>
       </c>
@@ -7997,8 +8301,11 @@
       <c r="AF67" s="3">
         <v>3</v>
       </c>
+      <c r="AG67" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="68" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>117</v>
       </c>
@@ -8095,8 +8402,11 @@
       <c r="AF68" s="3">
         <v>3</v>
       </c>
+      <c r="AG68" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="69" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>179</v>
       </c>
@@ -8193,8 +8503,11 @@
       <c r="AF69" s="3">
         <v>1</v>
       </c>
+      <c r="AG69" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="70" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>92</v>
       </c>
@@ -8291,8 +8604,11 @@
       <c r="AF70" s="3">
         <v>3</v>
       </c>
+      <c r="AG70" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="71" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>141</v>
       </c>
@@ -8389,8 +8705,11 @@
       <c r="AF71" s="3">
         <v>3</v>
       </c>
+      <c r="AG71" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="72" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>187</v>
       </c>
@@ -8487,8 +8806,11 @@
       <c r="AF72" s="3">
         <v>3</v>
       </c>
+      <c r="AG72" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="73" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>221</v>
       </c>
@@ -8585,8 +8907,11 @@
       <c r="AF73" s="3">
         <v>1</v>
       </c>
+      <c r="AG73" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="74" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>223</v>
       </c>
@@ -8600,7 +8925,7 @@
         <v>224</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F74" s="3">
         <v>3</v>
@@ -8683,8 +9008,11 @@
       <c r="AF74" s="3">
         <v>3</v>
       </c>
+      <c r="AG74" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="75" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>55</v>
       </c>
@@ -8781,8 +9109,11 @@
       <c r="AF75" s="3">
         <v>3</v>
       </c>
+      <c r="AG75" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="76" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>147</v>
       </c>
@@ -8879,8 +9210,11 @@
       <c r="AF76" s="3">
         <v>3</v>
       </c>
+      <c r="AG76" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>39</v>
       </c>
@@ -8977,8 +9311,11 @@
       <c r="AF77" s="3">
         <v>3</v>
       </c>
+      <c r="AG77" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="78" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>165</v>
       </c>
@@ -8992,7 +9329,7 @@
         <v>166</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F78" s="3">
         <v>3</v>
@@ -9075,8 +9412,11 @@
       <c r="AF78" s="3">
         <v>3</v>
       </c>
+      <c r="AG78" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="79" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>189</v>
       </c>
@@ -9173,8 +9513,11 @@
       <c r="AF79" s="3">
         <v>0</v>
       </c>
+      <c r="AG79" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="80" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>199</v>
       </c>
@@ -9188,7 +9531,7 @@
         <v>200</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F80" s="3">
         <v>3</v>
@@ -9271,8 +9614,11 @@
       <c r="AF80" s="3">
         <v>1</v>
       </c>
+      <c r="AG80" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="81" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>159</v>
       </c>
@@ -9369,8 +9715,11 @@
       <c r="AF81" s="3">
         <v>3</v>
       </c>
+      <c r="AG81" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="82" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>24</v>
       </c>
@@ -9467,8 +9816,11 @@
       <c r="AF82" s="3">
         <v>3</v>
       </c>
+      <c r="AG82" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="83" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>53</v>
       </c>
@@ -9482,7 +9834,7 @@
         <v>54</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F83" s="3">
         <v>3</v>
@@ -9565,8 +9917,11 @@
       <c r="AF83" s="3">
         <v>3</v>
       </c>
+      <c r="AG83" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="84" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>45</v>
       </c>
@@ -9580,7 +9935,7 @@
         <v>46</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F84" s="3">
         <v>3</v>
@@ -9663,8 +10018,11 @@
       <c r="AF84" s="3">
         <v>3</v>
       </c>
+      <c r="AG84" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="85" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>73</v>
       </c>
@@ -9761,8 +10119,11 @@
       <c r="AF85" s="3">
         <v>1</v>
       </c>
+      <c r="AG85" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="86" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>20</v>
       </c>
@@ -9776,7 +10137,7 @@
         <v>21</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F86" s="3">
         <v>3</v>
@@ -9859,8 +10220,11 @@
       <c r="AF86" s="3">
         <v>3</v>
       </c>
+      <c r="AG86" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="87" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>65</v>
       </c>
@@ -9957,8 +10321,11 @@
       <c r="AF87" s="3">
         <v>1</v>
       </c>
+      <c r="AG87" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="88" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>31</v>
       </c>
@@ -10055,8 +10422,11 @@
       <c r="AF88" s="3">
         <v>3</v>
       </c>
+      <c r="AG88" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="89" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>225</v>
       </c>
@@ -10153,8 +10523,11 @@
       <c r="AF89" s="3">
         <v>3</v>
       </c>
+      <c r="AG89" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="90" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>131</v>
       </c>
@@ -10251,8 +10624,11 @@
       <c r="AF90" s="3">
         <v>3</v>
       </c>
+      <c r="AG90" s="3">
+        <v>3</v>
+      </c>
     </row>
-    <row r="91" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>63</v>
       </c>
@@ -10349,8 +10725,11 @@
       <c r="AF91" s="3">
         <v>3</v>
       </c>
+      <c r="AG91" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="92" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>157</v>
       </c>
@@ -10364,7 +10743,7 @@
         <v>158</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="F92" s="3">
         <v>3</v>
@@ -10447,8 +10826,11 @@
       <c r="AF92" s="3">
         <v>3</v>
       </c>
+      <c r="AG92" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="93" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>163</v>
       </c>
@@ -10545,8 +10927,11 @@
       <c r="AF93" s="3">
         <v>1</v>
       </c>
+      <c r="AG93" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="94" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>37</v>
       </c>
@@ -10643,8 +11028,11 @@
       <c r="AF94" s="3">
         <v>3</v>
       </c>
+      <c r="AG94" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="95" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>83</v>
       </c>
@@ -10741,8 +11129,11 @@
       <c r="AF95" s="3">
         <v>3</v>
       </c>
+      <c r="AG95" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="96" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>137</v>
       </c>
@@ -10839,8 +11230,11 @@
       <c r="AF96" s="3">
         <v>3</v>
       </c>
+      <c r="AG96" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="97" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>51</v>
       </c>
@@ -10937,8 +11331,11 @@
       <c r="AF97" s="3">
         <v>1</v>
       </c>
+      <c r="AG97" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="98" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>71</v>
       </c>
@@ -11035,8 +11432,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>43</v>
       </c>
@@ -11133,8 +11533,11 @@
       <c r="AF99" s="3">
         <v>3</v>
       </c>
+      <c r="AG99" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="100" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>177</v>
       </c>
@@ -11231,8 +11634,11 @@
       <c r="AF100" s="3">
         <v>1</v>
       </c>
+      <c r="AG100" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="101" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>90</v>
       </c>
@@ -11329,8 +11735,11 @@
       <c r="AF101" s="3">
         <v>3</v>
       </c>
+      <c r="AG101" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="102" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>227</v>
       </c>
@@ -11427,8 +11836,11 @@
       <c r="AF102" s="3">
         <v>3</v>
       </c>
+      <c r="AG102" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="103" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>41</v>
       </c>
@@ -11525,8 +11937,11 @@
       <c r="AF103" s="3">
         <v>3</v>
       </c>
+      <c r="AG103" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="104" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>229</v>
       </c>
@@ -11540,7 +11955,7 @@
         <v>230</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="F104" s="3">
         <v>1</v>
@@ -11623,8 +12038,11 @@
       <c r="AF104" s="3">
         <v>3</v>
       </c>
+      <c r="AG104" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="105" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>100</v>
       </c>
@@ -11721,8 +12139,11 @@
       <c r="AF105" s="3">
         <v>3</v>
       </c>
+      <c r="AG105" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="106" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
         <v>88</v>
       </c>
@@ -11819,8 +12240,11 @@
       <c r="AF106" s="3">
         <v>3</v>
       </c>
+      <c r="AG106" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="107" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
         <v>22</v>
       </c>
@@ -11834,7 +12258,7 @@
         <v>23</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F107" s="3">
         <v>3</v>
@@ -11917,8 +12341,11 @@
       <c r="AF107" s="3">
         <v>1</v>
       </c>
+      <c r="AG107" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="108" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>127</v>
       </c>
@@ -12015,8 +12442,11 @@
       <c r="AF108" s="3">
         <v>1</v>
       </c>
+      <c r="AG108" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="109" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
         <v>129</v>
       </c>
@@ -12113,8 +12543,11 @@
       <c r="AF109" s="3">
         <v>1</v>
       </c>
+      <c r="AG109" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="110" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
         <v>16</v>
       </c>
@@ -12211,8 +12644,11 @@
       <c r="AF110" s="3">
         <v>3</v>
       </c>
+      <c r="AG110" s="3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="111" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
         <v>169</v>
       </c>
@@ -12309,8 +12745,11 @@
       <c r="AF111" s="3">
         <v>3</v>
       </c>
+      <c r="AG111" s="3">
+        <v>2</v>
+      </c>
     </row>
-    <row r="112" spans="1:32" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:33" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
         <v>49</v>
       </c>
@@ -12407,9 +12846,12 @@
       <c r="AF112" s="3">
         <v>3</v>
       </c>
+      <c r="AG112" s="3">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF112" xr:uid="{E1FAB33D-8E6A-CD48-A4EC-22CBB3EAF02F}"/>
+  <autoFilter ref="A1:AG113" xr:uid="{E1FAB33D-8E6A-CD48-A4EC-22CBB3EAF02F}"/>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{239E0C38-51C3-D54A-85FD-65F1A36BCC95}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{2E00E876-76AF-AB4C-A887-6FFA9FFBFCB6}"/>
@@ -12524,6 +12966,7 @@
     <hyperlink ref="D110" r:id="rId111" display="https://mail.yahoo.com/" xr:uid="{685601A4-8E6E-2647-8489-F4F4F6211245}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId112"/>
 </worksheet>
 </file>